--- a/artfynd/A 40412-2026 artfynd.xlsx
+++ b/artfynd/A 40412-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760077</v>
       </c>
       <c r="B2" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40412-2026 artfynd.xlsx
+++ b/artfynd/A 40412-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760077</v>
       </c>
       <c r="B2" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40412-2026 artfynd.xlsx
+++ b/artfynd/A 40412-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760077</v>
       </c>
       <c r="B2" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40412-2026 artfynd.xlsx
+++ b/artfynd/A 40412-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760077</v>
       </c>
       <c r="B2" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40412-2026 artfynd.xlsx
+++ b/artfynd/A 40412-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760077</v>
       </c>
       <c r="B2" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40412-2026 artfynd.xlsx
+++ b/artfynd/A 40412-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760077</v>
       </c>
       <c r="B2" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40412-2026 artfynd.xlsx
+++ b/artfynd/A 40412-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760077</v>
       </c>
       <c r="B2" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40412-2026 artfynd.xlsx
+++ b/artfynd/A 40412-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136760077</v>
       </c>
       <c r="B2" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
